--- a/data/dolar-index.xlsx
+++ b/data/dolar-index.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ipc-Patagonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">var%</t>
   </si>
 </sst>
 </file>
@@ -322,9 +319,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>46800</xdr:colOff>
+      <xdr:colOff>46440</xdr:colOff>
       <xdr:row>730</xdr:row>
-      <xdr:rowOff>118080</xdr:rowOff>
+      <xdr:rowOff>117720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -334,7 +331,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1606680" y="118506240"/>
-          <a:ext cx="360360" cy="280800"/>
+          <a:ext cx="360000" cy="280440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -578,8 +575,8 @@
       <c r="A2" s="3" t="n">
         <v>42705</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>26</v>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>100</v>
@@ -587,8 +584,8 @@
       <c r="D2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>100</v>
@@ -596,8 +593,8 @@
       <c r="G2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>26</v>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>100</v>
@@ -611,44 +608,44 @@
       <c r="L2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>26</v>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>26</v>
+      <c r="O2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>26</v>
+      <c r="Q2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>26</v>
+      <c r="S2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>26</v>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="W2" s="2" t="s">
-        <v>26</v>
+      <c r="W2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="Y2" s="2" t="s">
-        <v>26</v>
+      <c r="Y2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>100</v>
